--- a/TIME TABLE SAMPLE DATA/INPUTS/classrooms-template.xlsx
+++ b/TIME TABLE SAMPLE DATA/INPUTS/classrooms-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/INPUTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_2B59D2BFD3C0546BF9ADABD34C3088B352998D1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A9CA958-A526-4D39-82C2-C9DC6181A5AF}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_2B59D2BFD3C0546BF9ADABD34C3088B352998D1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE47E775-EC7A-4885-A372-1B0C701890B7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -389,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
@@ -460,6 +460,16 @@
         <v>1112</v>
       </c>
     </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TIME TABLE SAMPLE DATA/INPUTS/classrooms-template.xlsx
+++ b/TIME TABLE SAMPLE DATA/INPUTS/classrooms-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/INPUTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_2B59D2BFD3C0546BF9ADABD34C3088B352998D1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE47E775-EC7A-4885-A372-1B0C701890B7}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="11_2B59D2BFD3C0546BF9ADABD34C3088B352998D1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3FD786E-92E3-46D3-8728-1A9DA1D5D720}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,16 +20,88 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
   <si>
     <t>class_number</t>
+  </si>
+  <si>
+    <t>room_type</t>
+  </si>
+  <si>
+    <t>classroom</t>
+  </si>
+  <si>
+    <t>lab</t>
+  </si>
+  <si>
+    <t>capacity</t>
+  </si>
+  <si>
+    <t>section</t>
+  </si>
+  <si>
+    <t>strength</t>
+  </si>
+  <si>
+    <t>2C1</t>
+  </si>
+  <si>
+    <t>2C2</t>
+  </si>
+  <si>
+    <t>2C3</t>
+  </si>
+  <si>
+    <t>2C4</t>
+  </si>
+  <si>
+    <t>2C5</t>
+  </si>
+  <si>
+    <t>2C6</t>
+  </si>
+  <si>
+    <t>2C7</t>
+  </si>
+  <si>
+    <t>2G1</t>
+  </si>
+  <si>
+    <t>2G2</t>
+  </si>
+  <si>
+    <t>2G3</t>
+  </si>
+  <si>
+    <t>2G4</t>
+  </si>
+  <si>
+    <t>3C1</t>
+  </si>
+  <si>
+    <t>3C2</t>
+  </si>
+  <si>
+    <t>3C3</t>
+  </si>
+  <si>
+    <t>3C4</t>
+  </si>
+  <si>
+    <t>3C5</t>
+  </si>
+  <si>
+    <t>3G1</t>
+  </si>
+  <si>
+    <t>3G2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -41,6 +113,20 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -78,11 +164,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -389,88 +476,320 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1101</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1102</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>75</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1103</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>75</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1104</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>75</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1105</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>75</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1106</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>75</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1107</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>75</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1108</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>170</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1109</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>200</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1110</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>75</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1111</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1112</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1113</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>75</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1114</v>
       </c>
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>75</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2301</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2202</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2302</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TIME TABLE SAMPLE DATA/INPUTS/classrooms-template.xlsx
+++ b/TIME TABLE SAMPLE DATA/INPUTS/classrooms-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/INPUTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="11_2B59D2BFD3C0546BF9ADABD34C3088B352998D1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3FD786E-92E3-46D3-8728-1A9DA1D5D720}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="11_2B59D2BFD3C0546BF9ADABD34C3088B352998D1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{015BD1E9-B268-44AA-A721-A78D4660DE70}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -729,7 +729,7 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>75</v>
+        <v>3175</v>
       </c>
       <c r="D15" t="s">
         <v>20</v>
